--- a/data/results/stat_graz/p_hh.xlsx
+++ b/data/results/stat_graz/p_hh.xlsx
@@ -744,7 +744,7 @@
         <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="U2" t="n">
         <v>60</v>
@@ -887,7 +887,7 @@
         <v>75</v>
       </c>
       <c r="P3" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
@@ -911,7 +911,7 @@
         <v>75</v>
       </c>
       <c r="X3" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="Y3" t="n">
         <v>90</v>
